--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-core-organization-uf.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T08:09:55+00:00</t>
+    <t>2026-08-20T16:34:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-core-organization-uf.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T16:34:37+00:00</t>
+    <t>2026-08-21T09:28:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-core-organization-uf.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T09:28:33+00:00</t>
+    <t>2026-08-21T09:39:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-core-organization-uf.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-core-organization-uf.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$127</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3446" uniqueCount="640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4721" uniqueCount="712">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T09:39:43+00:00</t>
+    <t>2026-08-21T14:30:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1540,6 +1540,13 @@
     <t>Human contact for the organization.</t>
   </si>
   <si>
+    <t xml:space="preserve">profile:$this}
+</t>
+  </si>
+  <si>
+    <t>Slicing pour isoler la boîte MSS, conforme au profil standard AsMailboxMSSProfile</t>
+  </si>
+  <si>
     <t xml:space="preserve">org-3
 </t>
   </si>
@@ -1548,28 +1555,47 @@
 org-3:The telecom of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
   </si>
   <si>
+    <t>ORC-22?</t>
+  </si>
+  <si>
+    <t>.telecom</t>
+  </si>
+  <si>
+    <t>./ContactPoints</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss</t>
+  </si>
+  <si>
+    <t>mailbox-mss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss}
+</t>
+  </si>
+  <si>
+    <t>A contact detail for the organization</t>
+  </si>
+  <si>
     <t>boiteLettreMSS</t>
   </si>
   <si>
-    <t>ORC-22?</t>
-  </si>
-  <si>
-    <t>.telecom</t>
-  </si>
-  <si>
-    <t>./ContactPoints</t>
+    <t>Organization.telecom:mailbox-mss.id</t>
   </si>
   <si>
     <t>Organization.telecom.id</t>
   </si>
   <si>
+    <t>Organization.telecom:mailbox-mss.extension</t>
+  </si>
+  <si>
     <t>Organization.telecom.extension</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Organization.telecom.extension:emailType</t>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:emailType</t>
   </si>
   <si>
     <t>emailType</t>
@@ -1579,7 +1605,7 @@
 </t>
   </si>
   <si>
-    <t>Champs permettant de préciser le type d'email (MSSANTE | APICRYPT | OSM | AutreMessagerie) dont il est question dans le cas où le point de contact est un email.</t>
+    <t>Type of email | type de messagerie électronique</t>
   </si>
   <si>
     <t>Extension permettant d'indiquer le type d'adresse email d'un ContactPoint.
@@ -1587,7 +1613,188 @@
  This extension allows to specify the type of mail used to contact the person.</t>
   </si>
   <si>
-    <t>Organization.telecom.extension:ror-telecom-communication-channel</t>
+    <t>Organization.telecom:mailbox-mss.extension:emailType.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:emailType.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:emailType.url</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.url</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:emailType.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.value[x]</t>
+  </si>
+  <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="https://mos.esante.gouv.fr/NOS/TRE_R256-TypeMessagerie/FHIR/TRE-R256-TypeMessagerie"/&gt;
+  &lt;code value="MSSANTE"/&gt;
+  &lt;display value="MSSANTE"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-email-type|2.2.0</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata</t>
+  </si>
+  <si>
+    <t>as-mailbox-mss-metadata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-2}
+</t>
+  </si>
+  <si>
+    <t>L'attribut 'responsible' n'est pas disponible en accès libre.</t>
+  </si>
+  <si>
+    <t>Extension contenant les métadonnées de la mailbox mss.</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>typeBAL : Type de boîte aux lettres.
+Valeurs possibles : ORG | APP | PER | CAB</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.extension.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.url</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.extension.url</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J139-TypeBAL-RASS/FHIR/JDV-J139-TypeBAL-RASS|20231124120000</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.url</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible</t>
+  </si>
+  <si>
+    <t>responsible</t>
+  </si>
+  <si>
+    <t>responsable : Texte libre donnant les coordonnées de la (ou des) personne(s) responsable(s) au niveau opérationnel de la boîte aux lettres. Non renseigné pour les types de boîte aux lettres "PER".</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.url</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service</t>
+  </si>
+  <si>
+    <t>service</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.url</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge</t>
+  </si>
+  <si>
+    <t>listeRouge</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge.url</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.url</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:ror-telecom-communication-channel</t>
   </si>
   <si>
     <t>ror-telecom-communication-channel</t>
@@ -1603,7 +1810,7 @@
     <t>Extension créée dans le cadre du ROR spécifiant le canal ou la manière dont s'établit la communication</t>
   </si>
   <si>
-    <t>Organization.telecom.extension:ror-telecom-usage</t>
+    <t>Organization.telecom:mailbox-mss.extension:ror-telecom-usage</t>
   </si>
   <si>
     <t>ror-telecom-usage</t>
@@ -1619,7 +1826,7 @@
     <t>Extension créée dans le cadre du ROR qui précise l'utilisation du canal de communication</t>
   </si>
   <si>
-    <t>Organization.telecom.extension:ror-telecom-confidentiality-level</t>
+    <t>Organization.telecom:mailbox-mss.extension:ror-telecom-confidentiality-level</t>
   </si>
   <si>
     <t>ror-telecom-confidentiality-level</t>
@@ -1635,6 +1842,9 @@
     <t>Extension créée dans le cadre du ROR qui permet de définir le niveau de restriction de l'accès aux attributs de la classe Télécommunication.</t>
   </si>
   <si>
+    <t>Organization.telecom:mailbox-mss.system</t>
+  </si>
+  <si>
     <t>Organization.telecom.system</t>
   </si>
   <si>
@@ -1642,6 +1852,9 @@
   </si>
   <si>
     <t>Telecommunications form for contact point - what communications system is required to make use of the contact.</t>
+  </si>
+  <si>
+    <t>email</t>
   </si>
   <si>
     <t>Telecommunications form for contact point.</t>
@@ -1666,6 +1879,9 @@
     <t>./ContactPointType</t>
   </si>
   <si>
+    <t>Organization.telecom:mailbox-mss.value</t>
+  </si>
+  <si>
     <t>Organization.telecom.value</t>
   </si>
   <si>
@@ -1693,6 +1909,9 @@
     <t>./url</t>
   </si>
   <si>
+    <t>Organization.telecom:mailbox-mss.use</t>
+  </si>
+  <si>
     <t>Organization.telecom.use</t>
   </si>
   <si>
@@ -1724,6 +1943,9 @@
   </si>
   <si>
     <t>./ContactPointPurpose</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.rank</t>
   </si>
   <si>
     <t>Organization.telecom.rank</t>
@@ -1743,6 +1965,9 @@
   </si>
   <si>
     <t>ContactPoint.rank</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.period</t>
   </si>
   <si>
     <t>Organization.telecom.period</t>
@@ -2344,11 +2569,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO92"/>
+  <dimension ref="A1:AO127"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="55.20703125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="34.30078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="83.53515625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.3828125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="35.05078125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -2357,7 +2582,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="203.09375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2375,7 +2600,7 @@
     <col min="26" max="26" width="92.96875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="20.2734375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="64.12890625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="64.90625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -9774,7 +9999,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
         <v>478</v>
       </c>
@@ -9851,16 +10076,16 @@
         <v>77</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>77</v>
+        <v>484</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>77</v>
+        <v>485</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>478</v>
@@ -9872,35 +10097,37 @@
         <v>79</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>486</v>
+        <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="C65" s="2"/>
+        <v>478</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>492</v>
+      </c>
       <c r="D65" t="s" s="2">
         <v>77</v>
       </c>
@@ -9909,10 +10136,10 @@
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>77</v>
@@ -9921,16 +10148,20 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>104</v>
+        <v>493</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>105</v>
+        <v>494</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+        <v>481</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
       </c>
@@ -9978,31 +10209,31 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>107</v>
+        <v>478</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>77</v>
+        <v>486</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>77</v>
+        <v>487</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>77</v>
+        <v>495</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>77</v>
+        <v>488</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>108</v>
+        <v>489</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>77</v>
+        <v>490</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>77</v>
@@ -10010,10 +10241,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10021,10 +10252,10 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>492</v>
+        <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>77</v>
@@ -10036,13 +10267,13 @@
         <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>203</v>
+        <v>105</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>204</v>
+        <v>106</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10081,31 +10312,31 @@
         <v>77</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
@@ -10114,7 +10345,7 @@
         <v>77</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>77</v>
@@ -10125,23 +10356,21 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>494</v>
-      </c>
+        <v>499</v>
+      </c>
+      <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>78</v>
+        <v>500</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>77</v>
@@ -10153,13 +10382,13 @@
         <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>495</v>
+        <v>111</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>496</v>
+        <v>203</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>497</v>
+        <v>204</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10198,16 +10427,16 @@
         <v>77</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>118</v>
@@ -10240,15 +10469,15 @@
         <v>77</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>77</v>
@@ -10261,7 +10490,7 @@
         <v>88</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>77</v>
@@ -10270,13 +10499,13 @@
         <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10357,16 +10586,14 @@
         <v>77</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="C69" t="s" s="2">
-        <v>504</v>
-      </c>
+        <v>507</v>
+      </c>
+      <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
         <v>77</v>
       </c>
@@ -10378,7 +10605,7 @@
         <v>88</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>77</v>
@@ -10387,13 +10614,13 @@
         <v>77</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>505</v>
+        <v>104</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>506</v>
+        <v>105</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>507</v>
+        <v>106</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10444,19 +10671,19 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>77</v>
@@ -10465,7 +10692,7 @@
         <v>77</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>77</v>
@@ -10474,28 +10701,26 @@
         <v>77</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
         <v>508</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="C70" t="s" s="2">
         <v>509</v>
       </c>
+      <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>77</v>
@@ -10504,13 +10729,13 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>510</v>
+        <v>111</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>511</v>
+        <v>203</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>512</v>
+        <v>204</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10549,16 +10774,16 @@
         <v>77</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>118</v>
@@ -10593,10 +10818,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10616,25 +10841,27 @@
         <v>77</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>178</v>
+        <v>133</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>514</v>
+        <v>295</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>77</v>
+        <v>512</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>77</v>
@@ -10652,13 +10879,13 @@
         <v>77</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>169</v>
+        <v>77</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>516</v>
+        <v>77</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>517</v>
+        <v>77</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>77</v>
@@ -10676,42 +10903,42 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>518</v>
+        <v>299</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>519</v>
+        <v>77</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>520</v>
+        <v>77</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>521</v>
+        <v>201</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>522</v>
+        <v>77</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10719,35 +10946,31 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>524</v>
+        <v>303</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>527</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>77</v>
       </c>
@@ -10756,7 +10979,7 @@
         <v>77</v>
       </c>
       <c r="S72" t="s" s="2">
-        <v>77</v>
+        <v>515</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>77</v>
@@ -10771,13 +10994,11 @@
         <v>77</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>77</v>
+        <v>516</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>77</v>
@@ -10795,7 +11016,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>528</v>
+        <v>305</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10810,16 +11031,16 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>529</v>
+        <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>530</v>
+        <v>77</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>531</v>
+        <v>201</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>414</v>
+        <v>77</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>77</v>
@@ -10827,12 +11048,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>532</v>
+        <v>517</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="C73" s="2"/>
+        <v>499</v>
+      </c>
+      <c r="C73" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="D73" t="s" s="2">
         <v>77</v>
       </c>
@@ -10847,26 +11070,22 @@
         <v>77</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>178</v>
+        <v>519</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>533</v>
+        <v>520</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>536</v>
-      </c>
+        <v>521</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>77</v>
       </c>
@@ -10890,13 +11109,13 @@
         <v>77</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>169</v>
+        <v>77</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>537</v>
+        <v>77</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>538</v>
+        <v>77</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>77</v>
@@ -10914,31 +11133,31 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>539</v>
+        <v>118</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>540</v>
+        <v>77</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>541</v>
+        <v>77</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>542</v>
+        <v>77</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>77</v>
@@ -10946,10 +11165,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>543</v>
+        <v>522</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>543</v>
+        <v>507</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10969,20 +11188,18 @@
         <v>77</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>544</v>
+        <v>104</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>545</v>
+        <v>105</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>547</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>77</v>
@@ -11031,7 +11248,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>548</v>
+        <v>107</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11043,13 +11260,13 @@
         <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>108</v>
@@ -11063,21 +11280,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>549</v>
+        <v>523</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>549</v>
+        <v>509</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>77</v>
@@ -11086,18 +11303,20 @@
         <v>77</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>302</v>
+        <v>111</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>550</v>
+        <v>112</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -11134,43 +11353,43 @@
         <v>77</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>552</v>
+        <v>118</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>553</v>
+        <v>108</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>424</v>
+        <v>77</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>77</v>
@@ -11178,12 +11397,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>554</v>
+        <v>524</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="C76" s="2"/>
+        <v>509</v>
+      </c>
+      <c r="C76" t="s" s="2">
+        <v>525</v>
+      </c>
       <c r="D76" t="s" s="2">
         <v>77</v>
       </c>
@@ -11192,7 +11413,7 @@
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>77</v>
@@ -11204,20 +11425,16 @@
         <v>77</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>555</v>
+        <v>111</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>556</v>
+        <v>526</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>559</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>77</v>
       </c>
@@ -11265,7 +11482,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>554</v>
+        <v>118</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11274,33 +11491,33 @@
         <v>79</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>560</v>
+        <v>77</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>561</v>
+        <v>119</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>562</v>
+        <v>77</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>563</v>
+        <v>77</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>564</v>
+        <v>77</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>565</v>
+        <v>527</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>565</v>
+        <v>528</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11314,27 +11531,25 @@
         <v>88</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>566</v>
+        <v>104</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>567</v>
+        <v>105</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>568</v>
+        <v>106</v>
       </c>
       <c r="N77" s="2"/>
-      <c r="O77" t="s" s="2">
-        <v>569</v>
-      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>77</v>
       </c>
@@ -11382,7 +11597,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>565</v>
+        <v>107</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11394,19 +11609,19 @@
         <v>77</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>443</v>
+        <v>77</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>570</v>
+        <v>108</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>77</v>
@@ -11414,10 +11629,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>571</v>
+        <v>529</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>571</v>
+        <v>530</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11428,7 +11643,7 @@
         <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>77</v>
@@ -11440,13 +11655,13 @@
         <v>77</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>105</v>
+        <v>203</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>106</v>
+        <v>204</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11485,31 +11700,31 @@
         <v>77</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>77</v>
@@ -11518,7 +11733,7 @@
         <v>77</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>77</v>
@@ -11529,21 +11744,21 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>572</v>
+        <v>531</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>572</v>
+        <v>532</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>77</v>
@@ -11555,16 +11770,16 @@
         <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>112</v>
+        <v>295</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>113</v>
+        <v>296</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>114</v>
+        <v>297</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11572,7 +11787,7 @@
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>77</v>
+        <v>525</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>77</v>
@@ -11602,31 +11817,31 @@
         <v>77</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>118</v>
+        <v>299</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>77</v>
@@ -11635,7 +11850,7 @@
         <v>77</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>108</v>
+        <v>201</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>77</v>
@@ -11646,10 +11861,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>573</v>
+        <v>533</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>573</v>
+        <v>534</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11669,20 +11884,18 @@
         <v>77</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>104</v>
+        <v>383</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>574</v>
+        <v>303</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>576</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>77</v>
@@ -11707,13 +11920,11 @@
         <v>77</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>77</v>
+        <v>535</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>77</v>
@@ -11731,7 +11942,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>577</v>
+        <v>305</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11740,7 +11951,7 @@
         <v>88</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>578</v>
+        <v>77</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>101</v>
@@ -11763,12 +11974,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>579</v>
+        <v>536</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="C81" s="2"/>
+        <v>509</v>
+      </c>
+      <c r="C81" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="D81" t="s" s="2">
         <v>77</v>
       </c>
@@ -11786,20 +11999,18 @@
         <v>77</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>580</v>
+        <v>203</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>582</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>77</v>
@@ -11824,11 +12035,13 @@
         <v>77</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="Y81" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z81" t="s" s="2">
-        <v>453</v>
+        <v>77</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>77</v>
@@ -11846,19 +12059,19 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>583</v>
+        <v>118</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
@@ -11867,7 +12080,7 @@
         <v>77</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>77</v>
@@ -11878,10 +12091,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>584</v>
+        <v>537</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>584</v>
+        <v>528</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11901,20 +12114,18 @@
         <v>77</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>353</v>
+        <v>104</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>585</v>
+        <v>105</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>587</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>77</v>
@@ -11963,7 +12174,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>588</v>
+        <v>107</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11975,7 +12186,7 @@
         <v>77</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>77</v>
@@ -11984,7 +12195,7 @@
         <v>77</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>589</v>
+        <v>108</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>77</v>
@@ -11995,10 +12206,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>590</v>
+        <v>538</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>590</v>
+        <v>530</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12009,7 +12220,7 @@
         <v>78</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>77</v>
@@ -12018,20 +12229,18 @@
         <v>77</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>591</v>
+        <v>203</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>593</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>77</v>
@@ -12068,31 +12277,31 @@
         <v>77</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>594</v>
+        <v>118</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>77</v>
@@ -12101,7 +12310,7 @@
         <v>77</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>77</v>
@@ -12112,10 +12321,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>595</v>
+        <v>539</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>595</v>
+        <v>532</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12123,10 +12332,10 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>77</v>
@@ -12138,26 +12347,24 @@
         <v>77</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>596</v>
+        <v>133</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>597</v>
+        <v>295</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>598</v>
+        <v>296</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>600</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
-        <v>77</v>
+        <v>213</v>
       </c>
       <c r="S84" t="s" s="2">
         <v>77</v>
@@ -12199,19 +12406,19 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>595</v>
+        <v>299</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>77</v>
@@ -12220,7 +12427,7 @@
         <v>77</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>601</v>
+        <v>201</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>77</v>
@@ -12231,10 +12438,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>602</v>
+        <v>540</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>602</v>
+        <v>534</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12260,10 +12467,10 @@
         <v>104</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>105</v>
+        <v>303</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>106</v>
+        <v>304</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12314,7 +12521,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>107</v>
+        <v>305</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12326,7 +12533,7 @@
         <v>77</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>77</v>
@@ -12335,7 +12542,7 @@
         <v>77</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>108</v>
+        <v>201</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>77</v>
@@ -12346,21 +12553,23 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>603</v>
+        <v>541</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="C86" s="2"/>
+        <v>509</v>
+      </c>
+      <c r="C86" t="s" s="2">
+        <v>542</v>
+      </c>
       <c r="D86" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>77</v>
@@ -12375,14 +12584,12 @@
         <v>111</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>112</v>
+        <v>543</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>77</v>
@@ -12452,7 +12659,7 @@
         <v>77</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>77</v>
@@ -12463,46 +12670,42 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>604</v>
+        <v>544</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>604</v>
+        <v>528</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>605</v>
+        <v>77</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>606</v>
+        <v>105</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>77</v>
       </c>
@@ -12550,19 +12753,19 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>608</v>
+        <v>107</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>77</v>
@@ -12571,7 +12774,7 @@
         <v>77</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>201</v>
+        <v>108</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>77</v>
@@ -12582,10 +12785,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>609</v>
+        <v>545</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>609</v>
+        <v>530</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12596,7 +12799,7 @@
         <v>78</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>77</v>
@@ -12608,18 +12811,16 @@
         <v>77</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>383</v>
+        <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>610</v>
+        <v>203</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>611</v>
+        <v>204</v>
       </c>
       <c r="N88" s="2"/>
-      <c r="O88" t="s" s="2">
-        <v>612</v>
-      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>77</v>
       </c>
@@ -12643,43 +12844,43 @@
         <v>77</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>154</v>
+        <v>77</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>613</v>
+        <v>77</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>614</v>
+        <v>77</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>609</v>
+        <v>118</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>77</v>
@@ -12688,7 +12889,7 @@
         <v>77</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>615</v>
+        <v>77</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>77</v>
@@ -12699,10 +12900,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>616</v>
+        <v>546</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>616</v>
+        <v>532</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12710,7 +12911,7 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>88</v>
@@ -12725,24 +12926,24 @@
         <v>77</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>617</v>
+        <v>133</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>618</v>
+        <v>295</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" t="s" s="2">
-        <v>620</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q89" s="2"/>
       <c r="R89" t="s" s="2">
-        <v>77</v>
+        <v>542</v>
       </c>
       <c r="S89" t="s" s="2">
         <v>77</v>
@@ -12784,10 +12985,10 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>616</v>
+        <v>299</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>88</v>
@@ -12796,16 +12997,16 @@
         <v>77</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>621</v>
+        <v>77</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>622</v>
+        <v>201</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>77</v>
@@ -12816,10 +13017,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>623</v>
+        <v>547</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>623</v>
+        <v>534</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12830,7 +13031,7 @@
         <v>78</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>77</v>
@@ -12842,18 +13043,16 @@
         <v>77</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>479</v>
+        <v>104</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>624</v>
+        <v>303</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>625</v>
+        <v>304</v>
       </c>
       <c r="N90" s="2"/>
-      <c r="O90" t="s" s="2">
-        <v>626</v>
-      </c>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>77</v>
       </c>
@@ -12901,13 +13100,13 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>623</v>
+        <v>305</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>77</v>
@@ -12919,10 +13118,10 @@
         <v>77</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>627</v>
+        <v>77</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>628</v>
+        <v>201</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>77</v>
@@ -12933,12 +13132,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>629</v>
+        <v>548</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="C91" s="2"/>
+        <v>509</v>
+      </c>
+      <c r="C91" t="s" s="2">
+        <v>549</v>
+      </c>
       <c r="D91" t="s" s="2">
         <v>77</v>
       </c>
@@ -12959,18 +13160,16 @@
         <v>77</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>555</v>
+        <v>111</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>630</v>
+        <v>203</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>631</v>
+        <v>204</v>
       </c>
       <c r="N91" s="2"/>
-      <c r="O91" t="s" s="2">
-        <v>632</v>
-      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>77</v>
       </c>
@@ -13018,28 +13217,28 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>629</v>
+        <v>118</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>633</v>
+        <v>77</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>634</v>
+        <v>77</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>77</v>
@@ -13050,10 +13249,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>635</v>
+        <v>550</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>635</v>
+        <v>528</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13064,7 +13263,7 @@
         <v>78</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>77</v>
@@ -13076,18 +13275,16 @@
         <v>77</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>636</v>
+        <v>104</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>637</v>
+        <v>105</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>638</v>
+        <v>106</v>
       </c>
       <c r="N92" s="2"/>
-      <c r="O92" t="s" s="2">
-        <v>639</v>
-      </c>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>77</v>
       </c>
@@ -13135,19 +13332,19 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>635</v>
+        <v>107</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>77</v>
@@ -13165,8 +13362,4091 @@
         <v>77</v>
       </c>
     </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="C96" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="D96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
+      <c r="P98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
+      <c r="P100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C103" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="D103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C104" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="D104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C105" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="D105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="N105" s="2"/>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2"/>
+      <c r="P106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="P107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="108" hidden="true">
+      <c r="A108" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="P108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="109" hidden="true">
+      <c r="A109" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="O109" s="2"/>
+      <c r="P109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="110" hidden="true">
+      <c r="A110" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="N110" s="2"/>
+      <c r="O110" s="2"/>
+      <c r="P110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AO110" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="111" hidden="true">
+      <c r="A111" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="P111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="P112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AO112" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="113" hidden="true">
+      <c r="A113" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" s="2"/>
+      <c r="P113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO113" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O114" s="2"/>
+      <c r="P114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="115" hidden="true">
+      <c r="A115" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="O115" s="2"/>
+      <c r="P115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO115" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="116" hidden="true">
+      <c r="A116" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="O116" s="2"/>
+      <c r="P116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="Y116" s="2"/>
+      <c r="Z116" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO116" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="117" hidden="true">
+      <c r="A117" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="O117" s="2"/>
+      <c r="P117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO117" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="118" hidden="true">
+      <c r="A118" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="O118" s="2"/>
+      <c r="P118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO118" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="119" hidden="true">
+      <c r="A119" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="P119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO119" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="120" hidden="true">
+      <c r="A120" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N120" s="2"/>
+      <c r="O120" s="2"/>
+      <c r="P120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO120" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="121" hidden="true">
+      <c r="A121" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O121" s="2"/>
+      <c r="P121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO121" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="122" hidden="true">
+      <c r="A122" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O122" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="P122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AN122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO122" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="123" hidden="true">
+      <c r="A123" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="N123" s="2"/>
+      <c r="O123" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="P123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="AN123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO123" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="124" hidden="true">
+      <c r="A124" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="N124" s="2"/>
+      <c r="O124" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="P124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="AN124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO124" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="125" hidden="true">
+      <c r="A125" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="N125" s="2"/>
+      <c r="O125" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="P125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="AN125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO125" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="126" hidden="true">
+      <c r="A126" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="N126" s="2"/>
+      <c r="O126" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="P126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q126" s="2"/>
+      <c r="R126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="AN126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO126" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="127" hidden="true">
+      <c r="A127" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="N127" s="2"/>
+      <c r="O127" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="P127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO127" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AO92">
+  <autoFilter ref="A1:AO127">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13176,7 +17456,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI91">
+  <conditionalFormatting sqref="A2:AI126">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-core-organization-uf.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T14:30:36+00:00</t>
+    <t>2026-08-21T16:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-core-organization-uf.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-core-organization-uf.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4721" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4721" uniqueCount="714">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T16:03:39+00:00</t>
+    <t>2026-08-26T13:04:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -706,6 +706,136 @@
     <t>The date range that this organization should be considered available.</t>
   </si>
   <si>
+    <t>Organization.extension:usePeriod.id</t>
+  </si>
+  <si>
+    <t>Organization.extension.id</t>
+  </si>
+  <si>
+    <t>Organization.extension:usePeriod.extension</t>
+  </si>
+  <si>
+    <t>Organization.extension.extension</t>
+  </si>
+  <si>
+    <t>Organization.extension:usePeriod.url</t>
+  </si>
+  <si>
+    <t>Organization.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/organization-period</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Organization.extension:usePeriod.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ext-1
+</t>
+  </si>
+  <si>
+    <t>Organization.extension:usePeriod.value[x].id</t>
+  </si>
+  <si>
+    <t>Organization.extension.value[x].id</t>
+  </si>
+  <si>
+    <t>Organization.extension:usePeriod.value[x].extension</t>
+  </si>
+  <si>
+    <t>Organization.extension.value[x].extension</t>
+  </si>
+  <si>
+    <t>Organization.extension:usePeriod.value[x].start</t>
+  </si>
+  <si>
+    <t>Organization.extension.value[x].start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Starting time with inclusive boundary</t>
+  </si>
+  <si>
+    <t>The start of the period. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
+  </si>
+  <si>
+    <t>Period.start</t>
+  </si>
+  <si>
+    <t>ele-1
+per-1</t>
+  </si>
+  <si>
+    <t>DR.1</t>
+  </si>
+  <si>
+    <t>./low</t>
+  </si>
+  <si>
+    <t>Organization.extension:usePeriod.value[x].end</t>
+  </si>
+  <si>
+    <t>Organization.extension.value[x].end</t>
+  </si>
+  <si>
+    <t>End time with inclusive boundary, if not ongoing</t>
+  </si>
+  <si>
+    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
+  </si>
+  <si>
+    <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
+  </si>
+  <si>
+    <t>If the end of the period is missing, it means that the period is ongoing</t>
+  </si>
+  <si>
+    <t>Period.end</t>
+  </si>
+  <si>
+    <t>dateOuverture</t>
+  </si>
+  <si>
+    <t>DR.2</t>
+  </si>
+  <si>
+    <t>./high</t>
+  </si>
+  <si>
     <t>Organization.extension:openReason</t>
   </si>
   <si>
@@ -921,132 +1051,6 @@
   </si>
   <si>
     <t>dateOuverture (OI) + dateFermeture (OI)</t>
-  </si>
-  <si>
-    <t>Organization.extension:organization-period.id</t>
-  </si>
-  <si>
-    <t>Organization.extension.id</t>
-  </si>
-  <si>
-    <t>Organization.extension:organization-period.extension</t>
-  </si>
-  <si>
-    <t>Organization.extension.extension</t>
-  </si>
-  <si>
-    <t>Organization.extension:organization-period.url</t>
-  </si>
-  <si>
-    <t>Organization.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/organization-period</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>Organization.extension:organization-period.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.extension:organization-period.value[x].id</t>
-  </si>
-  <si>
-    <t>Organization.extension.value[x].id</t>
-  </si>
-  <si>
-    <t>Organization.extension:organization-period.value[x].extension</t>
-  </si>
-  <si>
-    <t>Organization.extension.value[x].extension</t>
-  </si>
-  <si>
-    <t>Organization.extension:organization-period.value[x].start</t>
-  </si>
-  <si>
-    <t>Organization.extension.value[x].start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Starting time with inclusive boundary</t>
-  </si>
-  <si>
-    <t>The start of the period. The boundary is inclusive.</t>
-  </si>
-  <si>
-    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
-  </si>
-  <si>
-    <t>Period.start</t>
-  </si>
-  <si>
-    <t>ele-1
-per-1</t>
-  </si>
-  <si>
-    <t>DR.1</t>
-  </si>
-  <si>
-    <t>./low</t>
-  </si>
-  <si>
-    <t>Organization.extension:organization-period.value[x].end</t>
-  </si>
-  <si>
-    <t>Organization.extension.value[x].end</t>
-  </si>
-  <si>
-    <t>End time with inclusive boundary, if not ongoing</t>
-  </si>
-  <si>
-    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
-  </si>
-  <si>
-    <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
-  </si>
-  <si>
-    <t>If the end of the period is missing, it means that the period is ongoing</t>
-  </si>
-  <si>
-    <t>Period.end</t>
-  </si>
-  <si>
-    <t>dateOuverture</t>
-  </si>
-  <si>
-    <t>DR.2</t>
-  </si>
-  <si>
-    <t>./high</t>
   </si>
   <si>
     <t>Organization.extension:ror-meta-comment</t>
@@ -1638,6 +1642,9 @@
   </si>
   <si>
     <t>Organization.telecom.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -5193,11 +5200,9 @@
         <v>221</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C23" t="s" s="2">
         <v>222</v>
       </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>77</v>
       </c>
@@ -5218,17 +5223,15 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>223</v>
+        <v>90</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>224</v>
+        <v>105</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -5277,19 +5280,19 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>205</v>
+        <v>107</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>77</v>
+        <v>211</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
@@ -5298,7 +5301,7 @@
         <v>77</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>77</v>
@@ -5309,14 +5312,12 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>77</v>
       </c>
@@ -5325,7 +5326,7 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>77</v>
@@ -5337,17 +5338,15 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>223</v>
+        <v>111</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -5384,19 +5383,19 @@
         <v>77</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>205</v>
+        <v>118</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5428,23 +5427,21 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>77</v>
@@ -5456,22 +5453,24 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>230</v>
+        <v>133</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>77</v>
+        <v>230</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>77</v>
@@ -5513,19 +5512,19 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>205</v>
+        <v>231</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>211</v>
+        <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>77</v>
@@ -5534,7 +5533,7 @@
         <v>77</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
@@ -5545,20 +5544,18 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="B26" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>234</v>
-      </c>
+      <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>88</v>
@@ -5573,13 +5570,13 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5630,19 +5627,19 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>77</v>
+        <v>238</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
@@ -5651,7 +5648,7 @@
         <v>77</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>77</v>
@@ -5662,14 +5659,12 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>77</v>
       </c>
@@ -5690,13 +5685,13 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>240</v>
+        <v>104</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>241</v>
+        <v>105</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>242</v>
+        <v>106</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5747,19 +5742,19 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>205</v>
+        <v>107</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
@@ -5768,7 +5763,7 @@
         <v>77</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>77</v>
@@ -5779,23 +5774,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
@@ -5807,15 +5800,17 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>245</v>
+        <v>111</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>246</v>
+        <v>112</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -5852,19 +5847,19 @@
         <v>77</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>205</v>
+        <v>118</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5873,7 +5868,7 @@
         <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>77</v>
+        <v>211</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>119</v>
@@ -5885,7 +5880,7 @@
         <v>77</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>77</v>
@@ -5896,14 +5891,12 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>77</v>
       </c>
@@ -5921,18 +5914,20 @@
         <v>77</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -5981,28 +5976,28 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>205</v>
+        <v>249</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>77</v>
+        <v>250</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>77</v>
+        <v>251</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>77</v>
+        <v>252</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -6016,11 +6011,9 @@
         <v>253</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C30" t="s" s="2">
         <v>254</v>
       </c>
+      <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>77</v>
       </c>
@@ -6038,23 +6031,27 @@
         <v>77</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q30" s="2"/>
+      <c r="Q30" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="R30" t="s" s="2">
         <v>77</v>
       </c>
@@ -6098,28 +6095,28 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>205</v>
+        <v>259</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>77</v>
+        <v>250</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>77</v>
+        <v>260</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>77</v>
+        <v>261</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>77</v>
+        <v>262</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -6130,13 +6127,13 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>202</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>77</v>
@@ -6146,7 +6143,7 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>77</v>
@@ -6158,15 +6155,17 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -6247,13 +6246,13 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>202</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>77</v>
@@ -6281,9 +6280,11 @@
         <v>266</v>
       </c>
       <c r="M32" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -6364,13 +6365,13 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>202</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>77</v>
@@ -6380,7 +6381,7 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>77</v>
@@ -6392,13 +6393,13 @@
         <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6458,7 +6459,7 @@
         <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>77</v>
+        <v>211</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>119</v>
@@ -6479,15 +6480,15 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>202</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>77</v>
@@ -6500,7 +6501,7 @@
         <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>77</v>
@@ -6509,13 +6510,13 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6581,7 +6582,7 @@
         <v>119</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>278</v>
+        <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>77</v>
@@ -6596,15 +6597,15 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>202</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>77</v>
@@ -6617,7 +6618,7 @@
         <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>77</v>
@@ -6626,13 +6627,13 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6698,7 +6699,7 @@
         <v>119</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>284</v>
+        <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>77</v>
@@ -6713,7 +6714,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>285</v>
       </c>
@@ -6734,7 +6735,7 @@
         <v>88</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>77</v>
@@ -6749,7 +6750,7 @@
         <v>288</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>220</v>
+        <v>289</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6832,12 +6833,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="C37" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="D37" t="s" s="2">
         <v>77</v>
       </c>
@@ -6858,13 +6861,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>104</v>
+        <v>292</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>105</v>
+        <v>293</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>106</v>
+        <v>294</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6915,19 +6918,19 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>107</v>
+        <v>205</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
@@ -6936,7 +6939,7 @@
         <v>77</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -6947,12 +6950,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="D38" t="s" s="2">
         <v>77</v>
       </c>
@@ -6961,7 +6966,7 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>77</v>
@@ -6973,13 +6978,13 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>111</v>
+        <v>297</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>203</v>
+        <v>298</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>204</v>
+        <v>299</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7018,19 +7023,19 @@
         <v>77</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>118</v>
+        <v>205</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -7062,21 +7067,23 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="D39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>77</v>
@@ -7088,24 +7095,22 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>133</v>
+        <v>302</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>298</v>
+        <v>77</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>77</v>
@@ -7147,19 +7152,19 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>299</v>
+        <v>205</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
@@ -7168,7 +7173,7 @@
         <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -7179,18 +7184,20 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="C40" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="D40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>88</v>
@@ -7205,13 +7212,13 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7262,19 +7269,19 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>305</v>
+        <v>205</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
@@ -7283,7 +7290,7 @@
         <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -7294,12 +7301,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="C41" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="D41" t="s" s="2">
         <v>77</v>
       </c>
@@ -7320,13 +7329,13 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>104</v>
+        <v>312</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>105</v>
+        <v>313</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>106</v>
+        <v>314</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7377,19 +7386,19 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>107</v>
+        <v>205</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
@@ -7398,7 +7407,7 @@
         <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -7407,26 +7416,28 @@
         <v>77</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>316</v>
+      </c>
       <c r="D42" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>77</v>
@@ -7435,17 +7446,15 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>111</v>
+        <v>317</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>112</v>
+        <v>318</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -7482,19 +7491,19 @@
         <v>77</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>118</v>
+        <v>205</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7503,19 +7512,19 @@
         <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>211</v>
+        <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>119</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>77</v>
+        <v>320</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>77</v>
@@ -7524,14 +7533,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="C43" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="D43" t="s" s="2">
         <v>77</v>
       </c>
@@ -7543,26 +7554,24 @@
         <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -7611,28 +7620,28 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>316</v>
+        <v>205</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>317</v>
+        <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>77</v>
+        <v>326</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>318</v>
+        <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>319</v>
+        <v>77</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
@@ -7641,14 +7650,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>77</v>
       </c>
@@ -7660,33 +7671,29 @@
         <v>88</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q44" t="s" s="2">
-        <v>325</v>
-      </c>
+      <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
         <v>77</v>
       </c>
@@ -7730,28 +7737,28 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>326</v>
+        <v>205</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>317</v>
+        <v>77</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>327</v>
+        <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>328</v>
+        <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>329</v>
+        <v>77</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
@@ -7762,13 +7769,13 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>202</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>77</v>
@@ -7790,13 +7797,13 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7879,13 +7886,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>202</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>77</v>
@@ -7907,13 +7914,13 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7979,7 +7986,7 @@
         <v>119</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>77</v>
@@ -7996,13 +8003,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>202</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>77</v>
@@ -8024,13 +8031,13 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8096,7 +8103,7 @@
         <v>119</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>77</v>
@@ -8113,10 +8120,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8142,16 +8149,16 @@
         <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -8200,7 +8207,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -8232,10 +8239,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8258,17 +8265,17 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -8305,7 +8312,7 @@
         <v>77</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AC49" s="2"/>
       <c r="AD49" t="s" s="2">
@@ -8315,7 +8322,7 @@
         <v>117</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8324,7 +8331,7 @@
         <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>101</v>
@@ -8333,27 +8340,27 @@
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>77</v>
@@ -8375,17 +8382,17 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -8434,7 +8441,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8443,33 +8450,33 @@
         <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8581,10 +8588,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8698,10 +8705,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8727,16 +8734,16 @@
         <v>178</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -8764,10 +8771,10 @@
         <v>169</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>77</v>
@@ -8785,7 +8792,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8806,7 +8813,7 @@
         <v>201</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
@@ -8817,10 +8824,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8843,19 +8850,19 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -8865,7 +8872,7 @@
         <v>77</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>77</v>
@@ -8883,10 +8890,10 @@
         <v>154</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -8904,7 +8911,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8922,10 +8929,10 @@
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -8936,10 +8943,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8965,16 +8972,16 @@
         <v>133</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -8984,10 +8991,10 @@
         <v>77</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>77</v>
@@ -9023,7 +9030,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -9041,13 +9048,13 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>77</v>
@@ -9055,10 +9062,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9084,13 +9091,13 @@
         <v>104</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9104,7 +9111,7 @@
         <v>77</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>77</v>
@@ -9140,7 +9147,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -9158,13 +9165,13 @@
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>77</v>
@@ -9172,10 +9179,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9198,16 +9205,16 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>302</v>
+        <v>234</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9257,7 +9264,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9269,19 +9276,19 @@
         <v>211</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>77</v>
@@ -9289,10 +9296,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9315,16 +9322,16 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9374,7 +9381,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9386,19 +9393,19 @@
         <v>211</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>77</v>
@@ -9406,10 +9413,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9432,70 +9439,70 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q59" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="R59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="P59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q59" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="R59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9513,24 +9520,24 @@
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9553,26 +9560,26 @@
         <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>77</v>
@@ -9594,16 +9601,16 @@
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>77</v>
@@ -9612,7 +9619,7 @@
         <v>117</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9630,27 +9637,27 @@
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>77</v>
@@ -9672,26 +9679,26 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="S61" t="s" s="2">
         <v>77</v>
@@ -9713,7 +9720,7 @@
       </c>
       <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>77</v>
@@ -9731,7 +9738,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9746,27 +9753,27 @@
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9792,16 +9799,16 @@
         <v>104</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -9850,7 +9857,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9859,22 +9866,22 @@
         <v>88</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>77</v>
@@ -9882,10 +9889,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9911,16 +9918,16 @@
         <v>104</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9969,7 +9976,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9990,7 +9997,7 @@
         <v>77</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>77</v>
@@ -10001,10 +10008,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10027,19 +10034,19 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
@@ -10076,10 +10083,10 @@
         <v>77</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>77</v>
@@ -10088,7 +10095,7 @@
         <v>117</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -10097,22 +10104,22 @@
         <v>79</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>77</v>
@@ -10120,13 +10127,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>77</v>
@@ -10148,19 +10155,19 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -10209,7 +10216,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -10218,22 +10225,22 @@
         <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>77</v>
@@ -10241,10 +10248,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10356,10 +10363,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10367,7 +10374,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>79</v>
@@ -10471,13 +10478,13 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>77</v>
@@ -10499,13 +10506,13 @@
         <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10588,10 +10595,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10703,10 +10710,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10818,10 +10825,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10847,13 +10854,13 @@
         <v>133</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>295</v>
+        <v>227</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>296</v>
+        <v>228</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>297</v>
+        <v>229</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10861,7 +10868,7 @@
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>77</v>
@@ -10903,7 +10910,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>299</v>
+        <v>231</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>88</v>
@@ -10935,10 +10942,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10964,10 +10971,10 @@
         <v>150</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>303</v>
+        <v>235</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>304</v>
+        <v>516</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10979,7 +10986,7 @@
         <v>77</v>
       </c>
       <c r="S72" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>77</v>
@@ -10998,7 +11005,7 @@
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>77</v>
@@ -11016,7 +11023,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>305</v>
+        <v>237</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -11048,13 +11055,13 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>77</v>
@@ -11076,13 +11083,13 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11165,10 +11172,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11280,10 +11287,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11397,13 +11404,13 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>77</v>
@@ -11428,7 +11435,7 @@
         <v>111</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="M76" t="s" s="2">
         <v>204</v>
@@ -11514,10 +11521,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11629,10 +11636,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11744,10 +11751,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11773,13 +11780,13 @@
         <v>133</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>295</v>
+        <v>227</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>296</v>
+        <v>228</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>297</v>
+        <v>229</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11787,7 +11794,7 @@
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>77</v>
@@ -11829,7 +11836,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>299</v>
+        <v>231</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>88</v>
@@ -11861,10 +11868,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11887,13 +11894,13 @@
         <v>77</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>303</v>
+        <v>235</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>304</v>
+        <v>516</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11924,7 +11931,7 @@
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>77</v>
@@ -11942,7 +11949,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>305</v>
+        <v>237</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11974,10 +11981,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C81" t="s" s="2">
         <v>213</v>
@@ -12091,10 +12098,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12206,10 +12213,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12321,10 +12328,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12350,13 +12357,13 @@
         <v>133</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>295</v>
+        <v>227</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>296</v>
+        <v>228</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>297</v>
+        <v>229</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12406,7 +12413,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>299</v>
+        <v>231</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>88</v>
@@ -12438,10 +12445,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12467,10 +12474,10 @@
         <v>104</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>303</v>
+        <v>235</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>304</v>
+        <v>516</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12521,7 +12528,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>305</v>
+        <v>237</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12553,13 +12560,13 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>77</v>
@@ -12584,7 +12591,7 @@
         <v>111</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="M86" t="s" s="2">
         <v>204</v>
@@ -12670,10 +12677,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12785,10 +12792,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12900,10 +12907,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12929,13 +12936,13 @@
         <v>133</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>295</v>
+        <v>227</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>296</v>
+        <v>228</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>297</v>
+        <v>229</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12943,7 +12950,7 @@
       </c>
       <c r="Q89" s="2"/>
       <c r="R89" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="S89" t="s" s="2">
         <v>77</v>
@@ -12985,7 +12992,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>299</v>
+        <v>231</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>88</v>
@@ -13017,10 +13024,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13046,10 +13053,10 @@
         <v>104</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>303</v>
+        <v>235</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>304</v>
+        <v>516</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13100,7 +13107,7 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>305</v>
+        <v>237</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13132,13 +13139,13 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D91" t="s" s="2">
         <v>77</v>
@@ -13249,10 +13256,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13364,10 +13371,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13479,10 +13486,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13508,13 +13515,13 @@
         <v>133</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>295</v>
+        <v>227</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>296</v>
+        <v>228</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>297</v>
+        <v>229</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13522,7 +13529,7 @@
       </c>
       <c r="Q94" s="2"/>
       <c r="R94" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="S94" t="s" s="2">
         <v>77</v>
@@ -13564,7 +13571,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>299</v>
+        <v>231</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>88</v>
@@ -13596,10 +13603,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13625,10 +13632,10 @@
         <v>104</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>303</v>
+        <v>235</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>304</v>
+        <v>516</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13679,7 +13686,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>305</v>
+        <v>237</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13711,13 +13718,13 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>77</v>
@@ -13828,10 +13835,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13943,10 +13950,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14058,10 +14065,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14087,13 +14094,13 @@
         <v>133</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>295</v>
+        <v>227</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>296</v>
+        <v>228</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>297</v>
+        <v>229</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14101,7 +14108,7 @@
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>77</v>
@@ -14143,7 +14150,7 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>299</v>
+        <v>231</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>88</v>
@@ -14175,10 +14182,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14201,13 +14208,13 @@
         <v>77</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>303</v>
+        <v>235</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>304</v>
+        <v>516</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14258,7 +14265,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>305</v>
+        <v>237</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14290,10 +14297,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14319,13 +14326,13 @@
         <v>133</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>295</v>
+        <v>227</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>296</v>
+        <v>228</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>297</v>
+        <v>229</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14333,7 +14340,7 @@
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>77</v>
@@ -14375,7 +14382,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>299</v>
+        <v>231</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>88</v>
@@ -14407,10 +14414,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14433,13 +14440,13 @@
         <v>77</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>303</v>
+        <v>235</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>304</v>
+        <v>516</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14490,7 +14497,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>305</v>
+        <v>237</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14522,13 +14529,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>77</v>
@@ -14550,13 +14557,13 @@
         <v>77</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14639,13 +14646,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>77</v>
@@ -14667,13 +14674,13 @@
         <v>77</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14756,13 +14763,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>77</v>
@@ -14784,13 +14791,13 @@
         <v>77</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14873,10 +14880,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14902,10 +14909,10 @@
         <v>178</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14917,7 +14924,7 @@
         <v>77</v>
       </c>
       <c r="S106" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="T106" t="s" s="2">
         <v>77</v>
@@ -14935,10 +14942,10 @@
         <v>169</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>77</v>
@@ -14956,7 +14963,7 @@
         <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -14965,7 +14972,7 @@
         <v>88</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>101</v>
@@ -14974,13 +14981,13 @@
         <v>77</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>77</v>
@@ -14988,10 +14995,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15017,16 +15024,16 @@
         <v>104</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>77</v>
@@ -15075,7 +15082,7 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -15090,16 +15097,16 @@
         <v>101</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>77</v>
@@ -15107,10 +15114,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15136,16 +15143,16 @@
         <v>178</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>77</v>
@@ -15173,10 +15180,10 @@
         <v>169</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>77</v>
@@ -15194,7 +15201,7 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -15212,13 +15219,13 @@
         <v>77</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>77</v>
@@ -15226,10 +15233,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15252,16 +15259,16 @@
         <v>89</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15311,7 +15318,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -15343,10 +15350,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15369,13 +15376,13 @@
         <v>89</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>302</v>
+        <v>234</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -15426,7 +15433,7 @@
         <v>77</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -15447,10 +15454,10 @@
         <v>201</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>77</v>
@@ -15458,10 +15465,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15484,19 +15491,19 @@
         <v>77</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>77</v>
@@ -15545,7 +15552,7 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -15554,22 +15561,22 @@
         <v>79</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>77</v>
@@ -15577,10 +15584,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15603,17 +15610,17 @@
         <v>89</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>77</v>
@@ -15662,7 +15669,7 @@
         <v>77</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -15680,10 +15687,10 @@
         <v>77</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>108</v>
@@ -15694,10 +15701,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15809,10 +15816,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15926,10 +15933,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15955,13 +15962,13 @@
         <v>104</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16011,7 +16018,7 @@
         <v>77</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -16020,7 +16027,7 @@
         <v>88</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>101</v>
@@ -16043,10 +16050,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16072,13 +16079,13 @@
         <v>133</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -16108,7 +16115,7 @@
       </c>
       <c r="Y116" s="2"/>
       <c r="Z116" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>77</v>
@@ -16126,7 +16133,7 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -16158,10 +16165,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16184,16 +16191,16 @@
         <v>89</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -16243,7 +16250,7 @@
         <v>77</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -16264,7 +16271,7 @@
         <v>77</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>77</v>
@@ -16275,10 +16282,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16304,13 +16311,13 @@
         <v>104</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -16360,7 +16367,7 @@
         <v>77</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -16392,10 +16399,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16418,19 +16425,19 @@
         <v>77</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>77</v>
@@ -16479,7 +16486,7 @@
         <v>77</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -16500,7 +16507,7 @@
         <v>77</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>77</v>
@@ -16511,10 +16518,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16626,10 +16633,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16743,14 +16750,14 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -16772,16 +16779,16 @@
         <v>111</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="N122" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>77</v>
@@ -16830,7 +16837,7 @@
         <v>77</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -16862,10 +16869,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16888,17 +16895,17 @@
         <v>77</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>77</v>
@@ -16926,10 +16933,10 @@
         <v>154</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>77</v>
@@ -16947,7 +16954,7 @@
         <v>77</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -16968,7 +16975,7 @@
         <v>77</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>77</v>
@@ -16979,10 +16986,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17005,17 +17012,17 @@
         <v>77</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>77</v>
@@ -17064,7 +17071,7 @@
         <v>77</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -17082,10 +17089,10 @@
         <v>77</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>77</v>
@@ -17096,10 +17103,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17122,17 +17129,17 @@
         <v>77</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>77</v>
@@ -17181,7 +17188,7 @@
         <v>77</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -17199,10 +17206,10 @@
         <v>77</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>77</v>
@@ -17213,10 +17220,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17239,17 +17246,17 @@
         <v>77</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>77</v>
@@ -17298,7 +17305,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -17316,10 +17323,10 @@
         <v>77</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>77</v>
@@ -17330,10 +17337,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17356,17 +17363,17 @@
         <v>77</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>77</v>
@@ -17415,7 +17422,7 @@
         <v>77</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
